--- a/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
+++ b/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T13:17:49+00:00</t>
+    <t>2026-08-19T13:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
+++ b/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T13:39:57+00:00</t>
+    <t>2026-08-19T14:02:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
+++ b/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T14:02:22+00:00</t>
+    <t>2026-08-19T15:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
+++ b/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T15:22:16+00:00</t>
+    <t>2026-08-19T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
+++ b/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T15:34:42+00:00</t>
+    <t>2026-08-19T15:52:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
+++ b/feature/ajouter-une-page-vers-la-spec-sso/ig/StructureDefinition-sas-cpts-healthcareservice-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T15:52:30+00:00</t>
+    <t>2026-08-19T16:05:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
